--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_6_13.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_6_13.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>222828.7510725866</v>
+        <v>213023.9515261771</v>
       </c>
     </row>
     <row r="7">
@@ -26288,10 +26288,10 @@
         <v>69879.81359544014</v>
       </c>
       <c r="K2" t="n">
+        <v>69879.81359544015</v>
+      </c>
+      <c r="L2" t="n">
         <v>69879.81359544014</v>
-      </c>
-      <c r="L2" t="n">
-        <v>69879.81359544015</v>
       </c>
       <c r="M2" t="n">
         <v>69879.81359544014</v>
@@ -26300,7 +26300,7 @@
         <v>69879.81359544014</v>
       </c>
       <c r="O2" t="n">
-        <v>69879.81359544015</v>
+        <v>69879.81359544014</v>
       </c>
       <c r="P2" t="n">
         <v>69879.81359544017</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
       <c r="C4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
       <c r="D4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
       <c r="E4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
       <c r="F4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
       <c r="G4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
       <c r="H4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
       <c r="I4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
       <c r="J4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
       <c r="K4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
       <c r="L4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
       <c r="M4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
       <c r="N4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
       <c r="O4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
       <c r="P4" t="n">
-        <v>32252.22165943392</v>
+        <v>33424.10713942487</v>
       </c>
     </row>
     <row r="5">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3999.991936006219</v>
+        <v>2828.106456015266</v>
       </c>
       <c r="C6" t="n">
-        <v>3999.991936006219</v>
+        <v>2828.106456015266</v>
       </c>
       <c r="D6" t="n">
-        <v>3999.991936006219</v>
+        <v>2828.106456015266</v>
       </c>
       <c r="E6" t="n">
-        <v>37627.59193600622</v>
+        <v>36455.70645601526</v>
       </c>
       <c r="F6" t="n">
-        <v>37627.59193600622</v>
+        <v>36455.70645601526</v>
       </c>
       <c r="G6" t="n">
-        <v>37627.59193600622</v>
+        <v>36455.70645601526</v>
       </c>
       <c r="H6" t="n">
-        <v>37627.59193600622</v>
+        <v>36455.70645601526</v>
       </c>
       <c r="I6" t="n">
-        <v>37627.59193600622</v>
+        <v>36455.70645601526</v>
       </c>
       <c r="J6" t="n">
-        <v>37627.59193600622</v>
+        <v>36455.70645601526</v>
       </c>
       <c r="K6" t="n">
-        <v>37627.59193600622</v>
+        <v>36455.70645601528</v>
       </c>
       <c r="L6" t="n">
-        <v>37627.59193600623</v>
+        <v>36455.70645601526</v>
       </c>
       <c r="M6" t="n">
-        <v>37627.59193600622</v>
+        <v>36455.70645601526</v>
       </c>
       <c r="N6" t="n">
-        <v>37627.59193600622</v>
+        <v>36455.70645601526</v>
       </c>
       <c r="O6" t="n">
-        <v>37627.59193600623</v>
+        <v>36455.70645601526</v>
       </c>
       <c r="P6" t="n">
-        <v>37627.59193600625</v>
+        <v>36455.70645601529</v>
       </c>
     </row>
   </sheetData>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26895,7 +26895,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -26904,37 +26904,37 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,19 +26947,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -26968,25 +26968,25 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
